--- a/data/trans_bre/P5B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Edad-trans_bre.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-23,46%</t>
+          <t>-23,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,91</t>
+          <t>-3,03; 5,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,56</t>
+          <t>-3,57; 1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,1</t>
+          <t>-1,93; 3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 7,03</t>
+          <t>-1,95; 6,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-62,69%</t>
+          <t>-62,83%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,68</t>
+          <t>-4,26; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,49</t>
+          <t>-1,94; 3,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,55</t>
+          <t>-0,77; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,61</t>
+          <t>-4,46; 0,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 69,15</t>
+          <t>-73,12; 65,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 363,21</t>
+          <t>-69,58; 352,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,96; 881,73</t>
+          <t>-62,04; 864,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 219,63</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>135,39%</t>
+          <t>136,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 9,18</t>
+          <t>0,54; 9,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,19</t>
+          <t>-1,29; 2,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,25</t>
+          <t>-0,9; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,58; —</t>
+          <t>-41,86; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,96</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>114,52%</t>
+          <t>115,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>834,74%</t>
+          <t>837,31%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,31</t>
+          <t>-2,01; 5,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,18</t>
+          <t>-0,97; 5,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,06</t>
+          <t>-2,96; 1,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 35,48</t>
+          <t>-1,1; 34,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,31; 361,22</t>
+          <t>-50,21; 356,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,93; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>267,31%</t>
+          <t>266,94%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,88</t>
+          <t>-0,86; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,69</t>
+          <t>-0,84; 1,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,83</t>
+          <t>-0,44; 1,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 18,1</t>
+          <t>-0,93; 14,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 132,85</t>
+          <t>-24,23; 123,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 158,5</t>
+          <t>-43,07; 200,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 289,72</t>
+          <t>-27,02; 274,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 1757,94</t>
+          <t>-65,67; 2583,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 5,09</t>
+          <t>-2,99; 5,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,53</t>
+          <t>-3,34; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,06</t>
+          <t>-1,63; 3,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,9</t>
+          <t>-1,92; 7,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,5</t>
+          <t>-4,5; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,47</t>
+          <t>-1,96; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,59</t>
+          <t>-0,9; 3,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,69</t>
+          <t>-4,4; 0,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,12; 65,49</t>
+          <t>-74,23; 62,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,58; 352,33</t>
+          <t>-69,74; 374,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,04; 864,13</t>
+          <t>-63,52; 855,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 269,87</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 9,08</t>
+          <t>0,78; 9,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,18</t>
+          <t>-1,29; 2,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,95</t>
+          <t>-1,02; 4,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,54; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,86; —</t>
+          <t>-41,32; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,24</t>
+          <t>-1,64; 5,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,19</t>
+          <t>-1,0; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,08</t>
+          <t>-2,87; 1,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 34,86</t>
+          <t>-1,12; 34,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 356,84</t>
+          <t>-46,95; 345,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,93; —</t>
+          <t>-69,12; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,8</t>
+          <t>-0,91; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,86</t>
+          <t>-0,95; 1,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,83</t>
+          <t>-0,41; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 14,85</t>
+          <t>-0,92; 17,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 123,67</t>
+          <t>-25,29; 118,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 200,01</t>
+          <t>-45,73; 217,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 274,41</t>
+          <t>-29,29; 319,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 2583,94</t>
+          <t>-63,75; 3077,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>109,26%</t>
+          <t>130,72%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 5,34</t>
+          <t>-2,95; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,82</t>
+          <t>-3,56; 1,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,2</t>
+          <t>-1,61; 3,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,0</t>
+          <t>-1,78; 8,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-62,83%</t>
+          <t>-63,0%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,55</t>
+          <t>-4,86; 1,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,24</t>
+          <t>-1,96; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,33</t>
+          <t>-0,9; 3,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,6</t>
+          <t>-4,96; 0,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,23; 62,1</t>
+          <t>-78,35; 69,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 374,09</t>
+          <t>-65,28; 363,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 855,41</t>
+          <t>-65,96; 737,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 269,87</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 9,66</t>
+          <t>0,42; 9,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,17</t>
+          <t>-1,29; 2,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,19</t>
+          <t>-0,82; 4,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,0</t>
+          <t>-2,41; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,32; —</t>
+          <t>-45,58; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,99</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>837,31%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,34</t>
+          <t>-2,06; 5,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,46</t>
+          <t>-1,25; 5,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,08</t>
+          <t>-2,98; 1,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 34,86</t>
+          <t>-1,23; 5,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 345,96</t>
+          <t>-52,31; 361,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,12; —</t>
+          <t>-100,0; 1094,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1286,59</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>266,94%</t>
+          <t>-13,03%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,8</t>
+          <t>-0,96; 2,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,84</t>
+          <t>-0,84; 1,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,97</t>
+          <t>-0,49; 1,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 17,02</t>
+          <t>-1,19; 1,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 118,67</t>
+          <t>-24,52; 132,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 217,33</t>
+          <t>-43,94; 193,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 319,89</t>
+          <t>-36,16; 275,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 3077,27</t>
+          <t>-67,5; 204,05</t>
         </is>
       </c>
     </row>
